--- a/erp-server/erp-server-file/src/main/resources/excel/wms/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/requisitionApplicationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27045" windowHeight="11850"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>单据编号</t>
   </si>
@@ -43,6 +43,12 @@
     <t>单据状态</t>
   </si>
   <si>
+    <t>拣货单生成状态</t>
+  </si>
+  <si>
+    <t>发货单生成状态</t>
+  </si>
+  <si>
     <t>来源单号</t>
   </si>
   <si>
@@ -107,6 +113,12 @@
   </si>
   <si>
     <t>{.statusName}</t>
+  </si>
+  <si>
+    <t>{.pickPushDownStatusName}</t>
+  </si>
+  <si>
+    <t>{.deliveryPushDownStatusName}</t>
   </si>
   <si>
     <t>{.sourceCode}</t>
@@ -195,6 +207,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF4A4A4A"/>
@@ -206,13 +225,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF4A4A4A"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -840,13 +852,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1197,36 +1209,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="16.125" customWidth="1"/>
     <col min="2" max="2" width="8.5" customWidth="1"/>
     <col min="3" max="3" width="27.375" customWidth="1"/>
     <col min="4" max="4" width="8.125" customWidth="1"/>
-    <col min="5" max="6" width="20.75" customWidth="1"/>
-    <col min="7" max="7" width="20.625" customWidth="1"/>
-    <col min="8" max="9" width="13.875" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="42" customWidth="1"/>
-    <col min="12" max="12" width="14.375" customWidth="1"/>
-    <col min="13" max="13" width="13.125" customWidth="1"/>
-    <col min="14" max="14" width="10.25" customWidth="1"/>
-    <col min="15" max="15" width="26.75" customWidth="1"/>
-    <col min="16" max="17" width="27.375" customWidth="1"/>
-    <col min="18" max="18" width="28" customWidth="1"/>
-    <col min="19" max="19" width="10.5" customWidth="1"/>
-    <col min="20" max="20" width="21.25" customWidth="1"/>
-    <col min="21" max="21" width="10.625" customWidth="1"/>
-    <col min="22" max="22" width="22.25" customWidth="1"/>
-    <col min="23" max="23" width="8.875" customWidth="1"/>
-    <col min="24" max="24" width="31.25" customWidth="1"/>
-    <col min="26" max="26" width="17.25" customWidth="1"/>
-    <col min="28" max="28" width="9.375" customWidth="1"/>
-    <col min="29" max="29" width="14.375" customWidth="1"/>
+    <col min="5" max="5" width="26.625" customWidth="1"/>
+    <col min="6" max="6" width="32.25" customWidth="1"/>
+    <col min="7" max="8" width="20.75" customWidth="1"/>
+    <col min="9" max="9" width="20.625" customWidth="1"/>
+    <col min="10" max="11" width="13.875" customWidth="1"/>
+    <col min="12" max="12" width="12.625" customWidth="1"/>
+    <col min="13" max="13" width="42" customWidth="1"/>
+    <col min="14" max="14" width="14.375" customWidth="1"/>
+    <col min="15" max="15" width="13.125" customWidth="1"/>
+    <col min="16" max="16" width="10.25" customWidth="1"/>
+    <col min="17" max="17" width="26.75" customWidth="1"/>
+    <col min="18" max="19" width="27.375" customWidth="1"/>
+    <col min="20" max="20" width="28" customWidth="1"/>
+    <col min="21" max="21" width="10.5" customWidth="1"/>
+    <col min="22" max="22" width="21.25" customWidth="1"/>
+    <col min="23" max="23" width="10.625" customWidth="1"/>
+    <col min="24" max="24" width="22.25" customWidth="1"/>
+    <col min="25" max="25" width="8.875" customWidth="1"/>
+    <col min="26" max="26" width="31.25" customWidth="1"/>
+    <col min="28" max="28" width="17.25" customWidth="1"/>
+    <col min="30" max="30" width="9.375" customWidth="1"/>
+    <col min="31" max="31" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:22">
+    <row r="1" s="1" customFormat="1" spans="1:24">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1245,19 +1259,19 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -1293,73 +1307,85 @@
       <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="W1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:22">
-      <c r="A2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="6" t="s">
+    <row r="2" s="2" customFormat="1" spans="1:24">
+      <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="D2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="F2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="H2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="J2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="K2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="L2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="M2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="N2" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="O2" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="P2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="Q2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="R2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="U2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" s="6" t="s">
+      <c r="S2" s="4" t="s">
         <v>42</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/requisitionApplicationExport.xlsx
@@ -43,10 +43,10 @@
     <t>单据状态</t>
   </si>
   <si>
-    <t>拣货单生成状态</t>
-  </si>
-  <si>
-    <t>发货单生成状态</t>
+    <t>拣货单生成</t>
+  </si>
+  <si>
+    <t>发货单生成</t>
   </si>
   <si>
     <t>来源单号</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/requisitionApplicationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/requisitionApplicationExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>单据编号</t>
   </si>
@@ -163,10 +163,13 @@
     <t>{.toWarehouseName}</t>
   </si>
   <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
+  </si>
+  <si>
     <t>{.handleUserName}</t>
-  </si>
-  <si>
-    <t>{.createTime}</t>
   </si>
   <si>
     <t>{.handleTime}</t>
@@ -1229,7 +1232,7 @@
     <col min="17" max="17" width="26.75" customWidth="1"/>
     <col min="18" max="19" width="27.375" customWidth="1"/>
     <col min="20" max="20" width="28" customWidth="1"/>
-    <col min="21" max="21" width="10.5" customWidth="1"/>
+    <col min="21" max="21" width="16.375" customWidth="1"/>
     <col min="22" max="22" width="21.25" customWidth="1"/>
     <col min="23" max="23" width="10.625" customWidth="1"/>
     <col min="24" max="24" width="22.25" customWidth="1"/>
@@ -1382,10 +1385,10 @@
         <v>45</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
